--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="114">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -286,18 +286,36 @@
     <t>fr-lm-entry.header.author[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur</t>
-  </si>
-  <si>
-    <t>Auteur(s) responsable(s) : Personne(s) ayant la responsabilité des informations fournies. Le rôle précis de l’auteur responsable dépend du contexte d’usage et du modèle concerné.</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.performer</t>
+    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -650,11 +668,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="24.421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.97265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.97265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -684,7 +702,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="24.421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.97265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1228,13 +1246,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1302,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1328,13 +1346,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1385,7 +1403,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1402,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1428,13 +1446,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1485,7 +1503,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1502,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1528,13 +1546,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1585,7 +1603,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1602,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1616,7 +1634,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1628,13 +1646,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1685,13 +1703,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1702,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1716,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1728,13 +1746,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1785,13 +1803,13 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
@@ -1802,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1816,7 +1834,7 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1831,10 +1849,10 @@
         <v>104</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1885,18 +1903,318 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AG12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH12" t="s" s="2">
+      <c r="B13" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
+      <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="116">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -367,6 +367,12 @@
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
 La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
 La partie en majuscules indique le code pays (ISO-3166)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.code</t>
+  </si>
+  <si>
+    <t>Type de l'entrée</t>
   </si>
 </sst>
 </file>
@@ -668,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.97265625" customWidth="true" bestFit="true"/>
@@ -2218,6 +2224,106 @@
         <v>73</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="114">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -367,12 +367,6 @@
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
 La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
 La partie en majuscules indique le code pays (ISO-3166)</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.code</t>
-  </si>
-  <si>
-    <t>Type de l'entrée</t>
   </si>
 </sst>
 </file>
@@ -674,7 +668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.97265625" customWidth="true" bestFit="true"/>
@@ -2224,106 +2218,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="115">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -292,30 +292,34 @@
     <t>fr-lm-entry.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -681,7 +685,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1646,13 +1650,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1720,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1746,13 +1750,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1803,7 +1807,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1820,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1846,13 +1850,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1903,7 +1907,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1920,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1946,13 +1950,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2003,7 +2007,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2020,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2046,13 +2050,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2103,7 +2107,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2120,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2146,13 +2150,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2203,7 +2207,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="125">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -292,7 +292,7 @@
     <t>fr-lm-entry.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -302,43 +302,61 @@
     <t>fr-lm-entry.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
     <t>L'auteur est un système</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
     <t>fr-lm-entry.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -355,11 +373,23 @@
     <t>Date/Heure de création par l'auteur</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.source</t>
+    <t>fr-lm-entry.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -672,11 +702,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.97265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.97265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.68359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.68359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -685,7 +715,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -699,14 +729,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.97265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1450,13 +1480,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1524,10 +1554,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1550,13 +1580,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1607,7 +1637,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1624,10 +1654,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1650,13 +1680,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1707,7 +1737,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1724,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1750,7 +1780,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>103</v>
@@ -1807,7 +1837,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1850,13 +1880,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1924,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1938,7 +1968,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -1950,13 +1980,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2007,13 +2037,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2024,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2038,7 +2068,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2050,13 +2080,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2107,13 +2137,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2124,10 +2154,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2138,7 +2168,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2153,10 +2183,10 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2207,18 +2237,418 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH15" t="s" s="2">
+      <c r="B16" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
+      <c r="H16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
